--- a/Datas/PastureData.xlsx
+++ b/Datas/PastureData.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="20">
   <si>
     <t>pastureName</t>
   </si>
@@ -76,6 +76,13 @@
   <si>
     <t>1003,2|1004,2</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>int</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>successTalk</t>
   </si>
 </sst>
 </file>
@@ -400,20 +407,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:K5"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="19.25" customWidth="1"/>
     <col min="2" max="2" width="9.625" customWidth="1"/>
     <col min="4" max="4" width="14.25" customWidth="1"/>
     <col min="5" max="5" width="12.125" customWidth="1"/>
-    <col min="6" max="6" width="14.25" customWidth="1"/>
-    <col min="7" max="7" width="7.375" customWidth="1"/>
-    <col min="8" max="8" width="11.375" customWidth="1"/>
-    <col min="9" max="9" width="10.5" customWidth="1"/>
+    <col min="6" max="7" width="14.25" customWidth="1"/>
+    <col min="8" max="8" width="7.375" customWidth="1"/>
+    <col min="9" max="9" width="11.375" customWidth="1"/>
+    <col min="10" max="10" width="10.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>6</v>
       </c>
@@ -421,7 +428,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -441,19 +448,22 @@
         <v>4</v>
       </c>
       <c r="G2" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="H2" t="s">
         <v>4</v>
       </c>
       <c r="I2" t="s">
+        <v>4</v>
+      </c>
+      <c r="J2" t="s">
         <v>15</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>0</v>
       </c>
@@ -473,19 +483,22 @@
         <v>11</v>
       </c>
       <c r="G3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H3" t="s">
         <v>12</v>
       </c>
-      <c r="H3" t="s">
+      <c r="I3" t="s">
         <v>8</v>
       </c>
-      <c r="I3" t="s">
+      <c r="J3" t="s">
         <v>13</v>
       </c>
-      <c r="J3" t="s">
+      <c r="K3" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -505,19 +518,22 @@
         <v>11</v>
       </c>
       <c r="G4">
+        <v>3014</v>
+      </c>
+      <c r="H4">
         <v>1</v>
       </c>
-      <c r="H4">
+      <c r="I4">
         <v>100</v>
       </c>
-      <c r="I4" t="s">
+      <c r="J4" t="s">
         <v>16</v>
       </c>
-      <c r="J4">
+      <c r="K4">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -537,15 +553,18 @@
         <v>11</v>
       </c>
       <c r="G5">
+        <v>3014</v>
+      </c>
+      <c r="H5">
         <v>2</v>
       </c>
-      <c r="H5">
+      <c r="I5">
         <v>200</v>
       </c>
-      <c r="I5" t="s">
+      <c r="J5" t="s">
         <v>17</v>
       </c>
-      <c r="J5">
+      <c r="K5">
         <v>4</v>
       </c>
     </row>
